--- a/Data Files/excelWrite.xlsx
+++ b/Data Files/excelWrite.xlsx
@@ -1,34 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diksha Thakur\Katalon Studio\katalondemo\myfirstKatalonProject\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{3E895BB2-1810-47F0-88A6-3AD6864560EA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{CA9A6E3C-7786-49EA-B6FA-93D9F97C8F70}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView windowHeight="13140" windowWidth="24240" xWindow="-120" xr2:uid="{506A85BF-F37F-4E75-BAC1-4FBE15A79EFD}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="write" r:id="rId1" sheetId="1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>username</t>
+    <t>EmployeeName</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>id</t>
+    <t>Diksha Thakur</t>
   </si>
 </sst>
 </file>
@@ -40,7 +53,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -85,9 +98,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
@@ -95,44 +108,44 @@
         <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -160,14 +173,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -195,9 +225,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -206,189 +253,181 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="9525">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="38100">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dir="5400000" dist="20000" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dir="5400000" dist="23000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dir="5400000" dist="23000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT h="25400" w="63500"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01EE264F-6708-4FAA-8F79-5A410D873650}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="67.140625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="12.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="15.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="15.7109375" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" width="16.140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
